--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_desktop_product_card.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_desktop_product_card.xlsx
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
